--- a/data/b2_primavera/B2 Primavera 09-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 09-2026.xlsx
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>6066</v>
+        <v>5366</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>32366</v>
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>6456</v>
+        <v>5956</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>25841</v>

--- a/data/b2_primavera/B2 Primavera 09-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 09-2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="DESPESAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3384,8 +3384,344 @@
         <v>6.689</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>37246</v>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>6644</v>
+      </c>
+      <c r="F98" s="9" t="n">
+        <v>30524</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="H98" s="11" t="n">
+        <v>6.186</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="n">
+        <v>7374</v>
+      </c>
+      <c r="D99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>1474</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>5899</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <v>5.9057</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>6.68</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>34068</v>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>3548</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>30512</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H100" s="11" t="n">
+        <v>4.488</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="n">
+        <v>7257</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>2226</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>5030</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>5.9772</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>6.689</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>30524</v>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>4753</v>
+      </c>
+      <c r="F102" s="9" t="n">
+        <v>25724</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="H102" s="11" t="n">
+        <v>6.186</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="n">
+        <v>5899</v>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>4697</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>5.9057</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>6.689</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>30512</v>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>2596</v>
+      </c>
+      <c r="F104" s="9" t="n">
+        <v>27911</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H104" s="11" t="n">
+        <v>4.483</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="n">
+        <v>5030</v>
+      </c>
+      <c r="D105" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>1785</v>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>13243</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>6.0675</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>6.685</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>25724</v>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>4696</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>20984</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="H106" s="11" t="n">
+        <v>6.187</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="n">
+        <v>4697</v>
+      </c>
+      <c r="D107" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>3606</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>5.9057</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>6.688</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>27911</v>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>25872</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H108" s="11" t="n">
+        <v>4.484</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="n">
+        <v>13243</v>
+      </c>
+      <c r="D109" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="13" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>11875</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>6.0675</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>6.69</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H97"/>
+  <autoFilter ref="A1:H109"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3401,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3882,8 +4218,35 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>6.113</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>61129.56</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>212090</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Alfa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3899,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3932,92 +4295,92 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1454.41</v>
+        <v>57825.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1124.97</v>
+        <v>2067.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>57557.61</v>
+        <v>3712.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3465.79</v>
+        <v>2677.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>2891.12</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7">
@@ -4026,52 +4389,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>14000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3600</v>
+        <v>1067.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2392.7</v>
+        <v>1486.15</v>
       </c>
     </row>
     <row r="10">
@@ -4089,7 +4452,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1111.06</v>
+        <v>1077.07</v>
       </c>
     </row>
     <row r="11">
@@ -4107,7 +4470,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>3943.17</v>
+        <v>3912.76</v>
       </c>
     </row>
     <row r="12">
@@ -4125,7 +4488,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>8979.440000000001</v>
+        <v>8973.01</v>
       </c>
     </row>
     <row r="13">
@@ -4143,25 +4506,25 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3303.56</v>
+        <v>3593.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>20020.04</v>
+        <v>1333.94</v>
       </c>
     </row>
     <row r="15">
@@ -4170,20 +4533,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Folha de pagamento</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Encargos (INSS e FGTS)</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>19985.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>Taxas de cartão</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
-        <v>3754.68</v>
+      <c r="D16" s="16" t="n">
+        <v>3811.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Taxas de cartão</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Taxas das maquininhas (semana)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>3701.59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D15"/>
+  <autoFilter ref="A1:D17"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Folha de pagamento,Aluguel,Energia elétrica,Água e esgoto,Taxas de cartão,Manutenção,Fretes,Sistemas e contabilidade,Marketing,Outras despesas"</formula1>
